--- a/output/topology_excel/7029.xlsx
+++ b/output/topology_excel/7029.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
         <v>9</v>
-      </c>
-      <c r="B8" t="n">
-        <v>11</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,24 +682,24 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
         <v>5</v>
       </c>
-      <c r="B23" t="n">
-        <v>6</v>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>261</v>
+        <v>193</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>124</v>
+        <v>261</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>237</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="F26" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>310</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="F29" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="F30" t="n">
-        <v>152</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,15 +1114,15 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>316</v>
+        <v>138</v>
       </c>
       <c r="F31" t="n">
-        <v>152</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
         <v>13</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="F32" t="n">
         <v>12</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>181</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B35" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,32 +1202,340 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>157</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>89</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>302</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>133</v>
+      </c>
+      <c r="F39" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>13</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B40" t="n">
+        <v>17</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>304</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" t="n">
+        <v>18</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>133</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>14</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>181</v>
-      </c>
-      <c r="F36" t="n">
-        <v>12</v>
+      <c r="B42" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>183</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>15</v>
+      </c>
+      <c r="B43" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>161</v>
+      </c>
+      <c r="F43" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" t="n">
+        <v>16</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>103</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B45" t="n">
+        <v>16</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>74</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B46" t="n">
+        <v>17</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>365</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" t="n">
+        <v>17</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>252</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="n">
+        <v>17</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>332</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>140</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="n">
+        <v>17</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>208</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/7029.xlsx
+++ b/output/topology_excel/7029.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,42 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
         </is>
       </c>
     </row>
@@ -481,6 +511,12 @@
       <c r="F2" t="n">
         <v>10</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +539,12 @@
       <c r="F3" t="n">
         <v>49</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +567,12 @@
       <c r="F4" t="n">
         <v>10</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +595,12 @@
       <c r="F5" t="n">
         <v>42</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +623,12 @@
       <c r="F6" t="n">
         <v>47</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +651,12 @@
       <c r="F7" t="n">
         <v>10</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +679,12 @@
       <c r="F8" t="n">
         <v>71</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +707,12 @@
       <c r="F9" t="n">
         <v>12</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +735,12 @@
       <c r="F10" t="n">
         <v>12</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +763,12 @@
       <c r="F11" t="n">
         <v>12</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +791,12 @@
       <c r="F12" t="n">
         <v>32</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -721,8 +817,14 @@
         <v>328</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +847,12 @@
       <c r="F14" t="n">
         <v>12</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +875,12 @@
       <c r="F15" t="n">
         <v>12</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +903,12 @@
       <c r="F16" t="n">
         <v>12</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +931,12 @@
       <c r="F17" t="n">
         <v>30</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +959,12 @@
       <c r="F18" t="n">
         <v>10</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +987,12 @@
       <c r="F19" t="n">
         <v>10</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1015,12 @@
       <c r="F20" t="n">
         <v>30</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +1043,12 @@
       <c r="F21" t="n">
         <v>30</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -919,8 +1069,14 @@
         <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1099,12 @@
       <c r="F23" t="n">
         <v>10</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -963,8 +1125,14 @@
         <v>261</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -985,8 +1153,14 @@
         <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>47</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1183,12 @@
       <c r="F26" t="n">
         <v>30</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1029,8 +1209,14 @@
         <v>299</v>
       </c>
       <c r="F27" t="n">
-        <v>85</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1239,12 @@
       <c r="F28" t="n">
         <v>10</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1267,12 @@
       <c r="F29" t="n">
         <v>10</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1295,12 @@
       <c r="F30" t="n">
         <v>10</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1323,12 @@
       <c r="F31" t="n">
         <v>10</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1351,12 @@
       <c r="F32" t="n">
         <v>12</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1379,12 @@
       <c r="F33" t="n">
         <v>12</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1407,12 @@
       <c r="F34" t="n">
         <v>10</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1205,8 +1433,14 @@
         <v>172</v>
       </c>
       <c r="F35" t="n">
-        <v>152</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1463,12 @@
       <c r="F36" t="n">
         <v>10</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1491,12 @@
       <c r="F37" t="n">
         <v>10</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1519,12 @@
       <c r="F38" t="n">
         <v>10</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1287,14 +1539,24 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F39" t="n">
-        <v>61</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G39" t="n">
+        <v>51</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1579,12 @@
       <c r="F40" t="n">
         <v>12</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1607,12 @@
       <c r="F41" t="n">
         <v>12</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1635,12 @@
       <c r="F42" t="n">
         <v>10</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1375,13 +1655,31 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>23</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>16</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>153</v>
+      </c>
+      <c r="L43" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -1397,7 +1695,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>103</v>
@@ -1405,13 +1703,23 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
+      <c r="G44" t="n">
+        <v>74</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1419,18 +1727,28 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>74</v>
+        <v>365</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
+      <c r="G45" t="n">
+        <v>252</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B46" t="n">
         <v>17</v>
@@ -1444,19 +1762,25 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" t="n">
         <v>8</v>
       </c>
-      <c r="B47" t="n">
-        <v>17</v>
-      </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>Opening</t>
@@ -1466,15 +1790,21 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>252</v>
+        <v>140</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="n">
         <v>17</v>
@@ -1488,55 +1818,17 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>332</v>
+        <v>208</v>
       </c>
       <c r="F48" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>2</v>
-      </c>
-      <c r="B49" t="n">
-        <v>8</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>140</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" t="n">
-        <v>17</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="n">
-        <v>208</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
